--- a/School_Reg.xlsx
+++ b/School_Reg.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -589,6 +589,49 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tanish</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12th-B</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20-08-2009</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>145</v>
+      </c>
+      <c r="G4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
